--- a/Fleet.xlsx
+++ b/Fleet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MohamedShakeel\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42BF41E3-FB35-43BD-82D5-A4004828EAB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5B784C0-B369-43E4-967F-AD642B4868C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14325" windowHeight="15480" xr2:uid="{EB5E0735-E981-4D65-8766-4471E111115C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB5E0735-E981-4D65-8766-4471E111115C}"/>
   </bookViews>
   <sheets>
     <sheet name="Vehicles &amp; others" sheetId="3" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1595" uniqueCount="610">
   <si>
     <t>QAIG-AT-18</t>
   </si>
@@ -1801,6 +1801,105 @@
   </si>
   <si>
     <t>JL7BCE1J0DK023330</t>
+  </si>
+  <si>
+    <t>F-31643</t>
+  </si>
+  <si>
+    <t>F-31644</t>
+  </si>
+  <si>
+    <t>F-31645</t>
+  </si>
+  <si>
+    <t>F-31646</t>
+  </si>
+  <si>
+    <t>F-31647</t>
+  </si>
+  <si>
+    <t>F-31648</t>
+  </si>
+  <si>
+    <t>F-31704</t>
+  </si>
+  <si>
+    <t>F-31705</t>
+  </si>
+  <si>
+    <t>F-31706</t>
+  </si>
+  <si>
+    <t>F-31707</t>
+  </si>
+  <si>
+    <t>QAIG-FL-023</t>
+  </si>
+  <si>
+    <t>QAIG-FL-016</t>
+  </si>
+  <si>
+    <t>QAIG-FL-022</t>
+  </si>
+  <si>
+    <t>QAIG-FL-021</t>
+  </si>
+  <si>
+    <t>QAIG-FL-015</t>
+  </si>
+  <si>
+    <t>QAIG-FL-024</t>
+  </si>
+  <si>
+    <t>QAIG-FL-017</t>
+  </si>
+  <si>
+    <t>QAIG-FL-019</t>
+  </si>
+  <si>
+    <t>QAIG-FL-020</t>
+  </si>
+  <si>
+    <t>QAIG-FL-018</t>
+  </si>
+  <si>
+    <t>XR702001008LA7961</t>
+  </si>
+  <si>
+    <t>XR702001007LA1473</t>
+  </si>
+  <si>
+    <t>XR702001009LA1687</t>
+  </si>
+  <si>
+    <t>XR702001009LA1699</t>
+  </si>
+  <si>
+    <t>XR702001007LA1459</t>
+  </si>
+  <si>
+    <t>XR702001008LA7963</t>
+  </si>
+  <si>
+    <t>XR1000-0016LA6705</t>
+  </si>
+  <si>
+    <t>XR1000-0016LA8025</t>
+  </si>
+  <si>
+    <t>XR1000-0016LA6696</t>
+  </si>
+  <si>
+    <t>XR1000-0016LA6704</t>
+  </si>
+  <si>
+    <t>CPCD70-XRW14B</t>
+  </si>
+  <si>
+    <t>CPCD100XRW14B</t>
+  </si>
+  <si>
+    <t>7T</t>
   </si>
 </sst>
 </file>
@@ -2280,8 +2379,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6460FE9F-EF3B-4D4D-BCC7-D162649A6FCD}">
-  <sheetPr codeName="Sheet4" filterMode="1"/>
-  <dimension ref="A1:L175"/>
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="A1:L181"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.85546875" style="9" customWidth="1"/>
@@ -2338,7 +2437,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>152</v>
       </c>
@@ -2373,7 +2472,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>152</v>
       </c>
@@ -2408,7 +2507,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>152</v>
       </c>
@@ -2443,7 +2542,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>152</v>
       </c>
@@ -2478,7 +2577,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>152</v>
       </c>
@@ -2513,7 +2612,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>152</v>
       </c>
@@ -2548,7 +2647,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>152</v>
       </c>
@@ -2583,7 +2682,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>152</v>
       </c>
@@ -2618,7 +2717,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>152</v>
       </c>
@@ -2653,7 +2752,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>152</v>
       </c>
@@ -2688,7 +2787,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>152</v>
       </c>
@@ -2723,7 +2822,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>152</v>
       </c>
@@ -2758,7 +2857,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>152</v>
       </c>
@@ -2793,7 +2892,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>152</v>
       </c>
@@ -2828,7 +2927,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>152</v>
       </c>
@@ -2863,7 +2962,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>152</v>
       </c>
@@ -2898,7 +2997,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>152</v>
       </c>
@@ -2933,7 +3032,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>152</v>
       </c>
@@ -2968,7 +3067,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>152</v>
       </c>
@@ -3003,7 +3102,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>152</v>
       </c>
@@ -3038,7 +3137,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>152</v>
       </c>
@@ -3073,7 +3172,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>152</v>
       </c>
@@ -3108,7 +3207,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>152</v>
       </c>
@@ -3143,7 +3242,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>152</v>
       </c>
@@ -3178,7 +3277,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>152</v>
       </c>
@@ -3213,7 +3312,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>152</v>
       </c>
@@ -3248,7 +3347,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>152</v>
       </c>
@@ -3283,7 +3382,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>152</v>
       </c>
@@ -3318,7 +3417,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>152</v>
       </c>
@@ -3353,7 +3452,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>152</v>
       </c>
@@ -3388,7 +3487,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>152</v>
       </c>
@@ -3423,7 +3522,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>152</v>
       </c>
@@ -3458,7 +3557,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>152</v>
       </c>
@@ -3493,7 +3592,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>152</v>
       </c>
@@ -3528,7 +3627,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>152</v>
       </c>
@@ -3563,7 +3662,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>152</v>
       </c>
@@ -3598,7 +3697,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>152</v>
       </c>
@@ -3633,7 +3732,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>152</v>
       </c>
@@ -3668,7 +3767,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>152</v>
       </c>
@@ -3703,7 +3802,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>152</v>
       </c>
@@ -3738,7 +3837,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>152</v>
       </c>
@@ -3773,7 +3872,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>152</v>
       </c>
@@ -3808,7 +3907,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>152</v>
       </c>
@@ -3843,7 +3942,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>152</v>
       </c>
@@ -3878,7 +3977,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>152</v>
       </c>
@@ -3913,7 +4012,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>152</v>
       </c>
@@ -3948,7 +4047,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>152</v>
       </c>
@@ -3983,7 +4082,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>152</v>
       </c>
@@ -4018,7 +4117,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>152</v>
       </c>
@@ -4053,7 +4152,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>152</v>
       </c>
@@ -4088,7 +4187,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>152</v>
       </c>
@@ -4123,7 +4222,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>152</v>
       </c>
@@ -4158,7 +4257,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>152</v>
       </c>
@@ -4193,7 +4292,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>152</v>
       </c>
@@ -4228,7 +4327,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>152</v>
       </c>
@@ -4263,7 +4362,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>152</v>
       </c>
@@ -4298,7 +4397,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>152</v>
       </c>
@@ -4333,7 +4432,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>152</v>
       </c>
@@ -4368,7 +4467,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>152</v>
       </c>
@@ -4403,7 +4502,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>152</v>
       </c>
@@ -4438,7 +4537,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>152</v>
       </c>
@@ -4473,7 +4572,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>152</v>
       </c>
@@ -4508,7 +4607,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>152</v>
       </c>
@@ -4543,7 +4642,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>152</v>
       </c>
@@ -4578,7 +4677,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>152</v>
       </c>
@@ -4613,7 +4712,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>152</v>
       </c>
@@ -4648,7 +4747,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>152</v>
       </c>
@@ -4682,7 +4781,7 @@
       </c>
       <c r="L68" s="4"/>
     </row>
-    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>530</v>
       </c>
@@ -4718,7 +4817,7 @@
       </c>
       <c r="L69" s="2"/>
     </row>
-    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>530</v>
       </c>
@@ -4754,7 +4853,7 @@
       </c>
       <c r="L70" s="2"/>
     </row>
-    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>530</v>
       </c>
@@ -4790,7 +4889,7 @@
       </c>
       <c r="L71" s="2"/>
     </row>
-    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>530</v>
       </c>
@@ -4826,7 +4925,7 @@
       </c>
       <c r="L72" s="2"/>
     </row>
-    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>530</v>
       </c>
@@ -4862,7 +4961,7 @@
       </c>
       <c r="L73" s="2"/>
     </row>
-    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>530</v>
       </c>
@@ -4898,7 +4997,7 @@
       </c>
       <c r="L74" s="2"/>
     </row>
-    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>530</v>
       </c>
@@ -4934,7 +5033,7 @@
       </c>
       <c r="L75" s="2"/>
     </row>
-    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>530</v>
       </c>
@@ -4970,7 +5069,7 @@
       </c>
       <c r="L76" s="2"/>
     </row>
-    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>530</v>
       </c>
@@ -5006,7 +5105,7 @@
       </c>
       <c r="L77" s="2"/>
     </row>
-    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>530</v>
       </c>
@@ -5042,7 +5141,7 @@
       </c>
       <c r="L78" s="2"/>
     </row>
-    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>530</v>
       </c>
@@ -5078,7 +5177,7 @@
       </c>
       <c r="L79" s="2"/>
     </row>
-    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>530</v>
       </c>
@@ -5114,7 +5213,7 @@
       </c>
       <c r="L80" s="2"/>
     </row>
-    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>531</v>
       </c>
@@ -5150,7 +5249,7 @@
       </c>
       <c r="L81" s="2"/>
     </row>
-    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>531</v>
       </c>
@@ -5186,7 +5285,7 @@
       </c>
       <c r="L82" s="2"/>
     </row>
-    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>531</v>
       </c>
@@ -5222,7 +5321,7 @@
       </c>
       <c r="L83" s="2"/>
     </row>
-    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>531</v>
       </c>
@@ -5258,7 +5357,7 @@
       </c>
       <c r="L84" s="2"/>
     </row>
-    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>531</v>
       </c>
@@ -5294,7 +5393,7 @@
       </c>
       <c r="L85" s="5"/>
     </row>
-    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>531</v>
       </c>
@@ -5330,7 +5429,7 @@
       </c>
       <c r="L86" s="5"/>
     </row>
-    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>531</v>
       </c>
@@ -5366,7 +5465,7 @@
       </c>
       <c r="L87" s="5"/>
     </row>
-    <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>153</v>
       </c>
@@ -5402,7 +5501,7 @@
       </c>
       <c r="L88" s="5"/>
     </row>
-    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>154</v>
       </c>
@@ -5438,7 +5537,7 @@
       </c>
       <c r="L89" s="5"/>
     </row>
-    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>154</v>
       </c>
@@ -5474,7 +5573,7 @@
       </c>
       <c r="L90" s="5"/>
     </row>
-    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>155</v>
       </c>
@@ -5510,7 +5609,7 @@
       </c>
       <c r="L91" s="5"/>
     </row>
-    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>155</v>
       </c>
@@ -5546,7 +5645,7 @@
       </c>
       <c r="L92" s="5"/>
     </row>
-    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>155</v>
       </c>
@@ -5582,7 +5681,7 @@
       </c>
       <c r="L93" s="5"/>
     </row>
-    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>155</v>
       </c>
@@ -5618,7 +5717,7 @@
       </c>
       <c r="L94" s="5"/>
     </row>
-    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>155</v>
       </c>
@@ -5654,7 +5753,7 @@
       </c>
       <c r="L95" s="5"/>
     </row>
-    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>156</v>
       </c>
@@ -5690,7 +5789,7 @@
       </c>
       <c r="L96" s="5"/>
     </row>
-    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>156</v>
       </c>
@@ -5726,7 +5825,7 @@
       </c>
       <c r="L97" s="5"/>
     </row>
-    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>157</v>
       </c>
@@ -5798,7 +5897,7 @@
       </c>
       <c r="L99" s="5"/>
     </row>
-    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>158</v>
       </c>
@@ -5834,7 +5933,7 @@
       </c>
       <c r="L100" s="5"/>
     </row>
-    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>158</v>
       </c>
@@ -5870,7 +5969,7 @@
       </c>
       <c r="L101" s="5"/>
     </row>
-    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>157</v>
       </c>
@@ -5978,7 +6077,7 @@
       </c>
       <c r="L104" s="5"/>
     </row>
-    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>157</v>
       </c>
@@ -6014,7 +6113,7 @@
       </c>
       <c r="L105" s="5"/>
     </row>
-    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>156</v>
       </c>
@@ -6050,7 +6149,7 @@
       </c>
       <c r="L106" s="5"/>
     </row>
-    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>156</v>
       </c>
@@ -6086,7 +6185,7 @@
       </c>
       <c r="L107" s="5"/>
     </row>
-    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>156</v>
       </c>
@@ -6122,7 +6221,7 @@
       </c>
       <c r="L108" s="5"/>
     </row>
-    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>156</v>
       </c>
@@ -6158,7 +6257,7 @@
       </c>
       <c r="L109" s="5"/>
     </row>
-    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>156</v>
       </c>
@@ -6194,7 +6293,7 @@
       </c>
       <c r="L110" s="5"/>
     </row>
-    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>156</v>
       </c>
@@ -6266,7 +6365,7 @@
       </c>
       <c r="L112" s="5"/>
     </row>
-    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>160</v>
       </c>
@@ -6301,7 +6400,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>161</v>
       </c>
@@ -6912,7 +7011,7 @@
       </c>
       <c r="L130" s="4"/>
     </row>
-    <row r="131" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>162</v>
       </c>
@@ -6946,7 +7045,7 @@
       </c>
       <c r="L131" s="4"/>
     </row>
-    <row r="132" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>162</v>
       </c>
@@ -6980,7 +7079,7 @@
       </c>
       <c r="L132" s="4"/>
     </row>
-    <row r="133" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>162</v>
       </c>
@@ -7014,7 +7113,7 @@
       </c>
       <c r="L133" s="4"/>
     </row>
-    <row r="134" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>162</v>
       </c>
@@ -7048,7 +7147,7 @@
       </c>
       <c r="L134" s="4"/>
     </row>
-    <row r="135" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>162</v>
       </c>
@@ -7082,7 +7181,7 @@
       </c>
       <c r="L135" s="4"/>
     </row>
-    <row r="136" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>162</v>
       </c>
@@ -7116,7 +7215,7 @@
       </c>
       <c r="L136" s="4"/>
     </row>
-    <row r="137" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>162</v>
       </c>
@@ -7150,7 +7249,7 @@
       </c>
       <c r="L137" s="4"/>
     </row>
-    <row r="138" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>162</v>
       </c>
@@ -7184,7 +7283,7 @@
       </c>
       <c r="L138" s="4"/>
     </row>
-    <row r="139" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>162</v>
       </c>
@@ -7218,7 +7317,7 @@
       </c>
       <c r="L139" s="4"/>
     </row>
-    <row r="140" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>162</v>
       </c>
@@ -7252,7 +7351,7 @@
       </c>
       <c r="L140" s="4"/>
     </row>
-    <row r="141" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>162</v>
       </c>
@@ -7286,7 +7385,7 @@
       </c>
       <c r="L141" s="4"/>
     </row>
-    <row r="142" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>162</v>
       </c>
@@ -7320,7 +7419,7 @@
       </c>
       <c r="L142" s="4"/>
     </row>
-    <row r="143" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>162</v>
       </c>
@@ -7354,7 +7453,7 @@
       </c>
       <c r="L143" s="4"/>
     </row>
-    <row r="144" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>162</v>
       </c>
@@ -7388,7 +7487,7 @@
       </c>
       <c r="L144" s="4"/>
     </row>
-    <row r="145" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>162</v>
       </c>
@@ -7422,7 +7521,7 @@
       </c>
       <c r="L145" s="4"/>
     </row>
-    <row r="146" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>152</v>
       </c>
@@ -7456,7 +7555,7 @@
       </c>
       <c r="L146" s="4"/>
     </row>
-    <row r="147" spans="1:12" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>152</v>
       </c>
@@ -7492,7 +7591,7 @@
       </c>
       <c r="L147" s="5"/>
     </row>
-    <row r="148" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>152</v>
       </c>
@@ -7526,7 +7625,7 @@
       </c>
       <c r="L148" s="4"/>
     </row>
-    <row r="149" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>152</v>
       </c>
@@ -7560,7 +7659,7 @@
       </c>
       <c r="L149" s="4"/>
     </row>
-    <row r="150" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" s="9" t="s">
         <v>152</v>
       </c>
@@ -7592,7 +7691,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="151" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" s="9" t="s">
         <v>152</v>
       </c>
@@ -7624,7 +7723,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="152" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" s="9" t="s">
         <v>152</v>
       </c>
@@ -7656,7 +7755,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="153" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" s="9" t="s">
         <v>152</v>
       </c>
@@ -7688,7 +7787,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="154" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" s="9" t="s">
         <v>152</v>
       </c>
@@ -7720,7 +7819,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="155" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" s="9" t="s">
         <v>152</v>
       </c>
@@ -7752,7 +7851,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="156" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" s="9" t="s">
         <v>152</v>
       </c>
@@ -7784,7 +7883,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="157" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" s="9" t="s">
         <v>152</v>
       </c>
@@ -7816,7 +7915,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="158" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" s="9" t="s">
         <v>152</v>
       </c>
@@ -7848,7 +7947,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="159" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" s="9" t="s">
         <v>152</v>
       </c>
@@ -7880,7 +7979,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="160" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" s="9" t="s">
         <v>152</v>
       </c>
@@ -7912,7 +8011,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="161" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" s="9" t="s">
         <v>152</v>
       </c>
@@ -7944,7 +8043,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="162" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" s="9" t="s">
         <v>152</v>
       </c>
@@ -7976,7 +8075,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="163" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" s="9" t="s">
         <v>152</v>
       </c>
@@ -8008,7 +8107,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="164" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" s="9" t="s">
         <v>152</v>
       </c>
@@ -8040,7 +8139,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="165" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" s="9" t="s">
         <v>152</v>
       </c>
@@ -8072,7 +8171,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="166" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" s="9" t="s">
         <v>152</v>
       </c>
@@ -8104,7 +8203,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="167" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" s="9" t="s">
         <v>152</v>
       </c>
@@ -8168,7 +8267,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="169" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" s="9" t="s">
         <v>531</v>
       </c>
@@ -8200,7 +8299,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="170" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" s="9" t="s">
         <v>531</v>
       </c>
@@ -8232,7 +8331,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="171" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" s="9" t="s">
         <v>531</v>
       </c>
@@ -8264,23 +8363,302 @@
         <v>138</v>
       </c>
     </row>
-    <row r="172" spans="1:11" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="1:11" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="1:11" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="1:11" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A172" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="E172" s="3">
+        <v>80282</v>
+      </c>
+      <c r="F172" s="11">
+        <v>2025</v>
+      </c>
+      <c r="G172" s="9" t="s">
+        <v>607</v>
+      </c>
+      <c r="H172" s="11" t="s">
+        <v>609</v>
+      </c>
+      <c r="I172" s="9" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A173" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="E173" s="3">
+        <v>80265</v>
+      </c>
+      <c r="F173" s="11">
+        <v>2025</v>
+      </c>
+      <c r="G173" s="9" t="s">
+        <v>607</v>
+      </c>
+      <c r="H173" s="11" t="s">
+        <v>609</v>
+      </c>
+      <c r="I173" s="9" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A174" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="E174" s="3">
+        <v>80281</v>
+      </c>
+      <c r="F174" s="11">
+        <v>2025</v>
+      </c>
+      <c r="G174" s="9" t="s">
+        <v>607</v>
+      </c>
+      <c r="H174" s="11" t="s">
+        <v>609</v>
+      </c>
+      <c r="I174" s="9" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A175" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="E175" s="3">
+        <v>80280</v>
+      </c>
+      <c r="F175" s="11">
+        <v>2025</v>
+      </c>
+      <c r="G175" s="9" t="s">
+        <v>607</v>
+      </c>
+      <c r="H175" s="11" t="s">
+        <v>609</v>
+      </c>
+      <c r="I175" s="9" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A176" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="E176" s="3">
+        <v>80263</v>
+      </c>
+      <c r="F176" s="11">
+        <v>2025</v>
+      </c>
+      <c r="G176" s="9" t="s">
+        <v>607</v>
+      </c>
+      <c r="H176" s="11" t="s">
+        <v>609</v>
+      </c>
+      <c r="I176" s="9" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A177" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="E177" s="3">
+        <v>80283</v>
+      </c>
+      <c r="F177" s="11">
+        <v>2025</v>
+      </c>
+      <c r="G177" s="9" t="s">
+        <v>607</v>
+      </c>
+      <c r="H177" s="11" t="s">
+        <v>609</v>
+      </c>
+      <c r="I177" s="9" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A178" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="E178" s="3">
+        <v>80266</v>
+      </c>
+      <c r="F178" s="11">
+        <v>2025</v>
+      </c>
+      <c r="G178" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="H178" s="11" t="s">
+        <v>570</v>
+      </c>
+      <c r="I178" s="9" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A179" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="D179" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="E179" s="3">
+        <v>80268</v>
+      </c>
+      <c r="F179" s="11">
+        <v>2025</v>
+      </c>
+      <c r="G179" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="H179" s="11" t="s">
+        <v>570</v>
+      </c>
+      <c r="I179" s="9" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A180" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="D180" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="E180" s="3">
+        <v>80270</v>
+      </c>
+      <c r="F180" s="11">
+        <v>2025</v>
+      </c>
+      <c r="G180" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="H180" s="11" t="s">
+        <v>570</v>
+      </c>
+      <c r="I180" s="9" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A181" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="D181" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="E181" s="3">
+        <v>80267</v>
+      </c>
+      <c r="F181" s="11">
+        <v>2025</v>
+      </c>
+      <c r="G181" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="H181" s="11" t="s">
+        <v>570</v>
+      </c>
+      <c r="I181" s="9" t="s">
+        <v>606</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <protectedRanges>
     <protectedRange algorithmName="SHA-512" hashValue="WRwemcA0nyhlBsNJB+ZrdRdmiulp5J6snsQZWL5Ah84Ed5Vozay/STzz6Yal5yBJ6ZZSR7Wbira9Zl6KkC6oHw==" saltValue="VcbLbYiFYBn8Dk3MVK5/Wg==" spinCount="100000" sqref="B106:B112" name="Range1_2"/>
   </protectedRanges>
-  <autoFilter ref="A1:M175" xr:uid="{6460FE9F-EF3B-4D4D-BCC7-D162649A6FCD}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="PICKUP TRUCK-CANTER 3.0 Ton"/>
-        <filter val="TRUCK"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M175" xr:uid="{6460FE9F-EF3B-4D4D-BCC7-D162649A6FCD}"/>
   <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="duplicateValues" dxfId="2" priority="5"/>
   </conditionalFormatting>
@@ -8295,6 +8673,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cf10023c-c1e1-4ca5-baf6-bad6626b84e9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_Flow_SignoffStatus xmlns="cf10023c-c1e1-4ca5-baf6-bad6626b84e9" xsi:nil="true"/>
+    <TaxCatchAll xmlns="40b16217-7e26-4dce-af97-68eaad0f1932" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CD0C5713D8B49840BA44FC47BC25FC9F" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d6c26ebffaa8bbd830e647f783d3198d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cf10023c-c1e1-4ca5-baf6-bad6626b84e9" xmlns:ns3="40b16217-7e26-4dce-af97-68eaad0f1932" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f461dd4a85cef57f3309d1104a6214f5" ns2:_="" ns3:_="">
     <xsd:import namespace="cf10023c-c1e1-4ca5-baf6-bad6626b84e9"/>
@@ -8529,28 +8928,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6269017F-E5DB-403C-81C5-BBF155D4F583}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cf10023c-c1e1-4ca5-baf6-bad6626b84e9"/>
+    <ds:schemaRef ds:uri="40b16217-7e26-4dce-af97-68eaad0f1932"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cf10023c-c1e1-4ca5-baf6-bad6626b84e9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_Flow_SignoffStatus xmlns="cf10023c-c1e1-4ca5-baf6-bad6626b84e9" xsi:nil="true"/>
-    <TaxCatchAll xmlns="40b16217-7e26-4dce-af97-68eaad0f1932" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{172B3EEB-21ED-4F96-BCDA-03252FF4BB1C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5A73F1C-4F4E-45A2-8E7F-3EB53382C2D3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8567,23 +8964,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{172B3EEB-21ED-4F96-BCDA-03252FF4BB1C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6269017F-E5DB-403C-81C5-BBF155D4F583}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="cf10023c-c1e1-4ca5-baf6-bad6626b84e9"/>
-    <ds:schemaRef ds:uri="40b16217-7e26-4dce-af97-68eaad0f1932"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Fleet.xlsx
+++ b/Fleet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MohamedShakeel\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5B784C0-B369-43E4-967F-AD642B4868C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95BB45E5-B1DD-43FE-9E68-351B02C9D9F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB5E0735-E981-4D65-8766-4471E111115C}"/>
+    <workbookView xWindow="1785" yWindow="225" windowWidth="13530" windowHeight="15345" xr2:uid="{EB5E0735-E981-4D65-8766-4471E111115C}"/>
   </bookViews>
   <sheets>
     <sheet name="Vehicles &amp; others" sheetId="3" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1595" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="615">
   <si>
     <t>QAIG-AT-18</t>
   </si>
@@ -1900,6 +1900,21 @@
   </si>
   <si>
     <t>7T</t>
+  </si>
+  <si>
+    <t>REACH STACKER</t>
+  </si>
+  <si>
+    <t>KALMAR</t>
+  </si>
+  <si>
+    <t>DRU450-6255</t>
+  </si>
+  <si>
+    <t>A69523-1000TY874</t>
+  </si>
+  <si>
+    <t>ST-31041</t>
   </si>
 </sst>
 </file>
@@ -2380,7 +2395,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6460FE9F-EF3B-4D4D-BCC7-D162649A6FCD}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:L181"/>
+  <dimension ref="A1:L182"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.85546875" style="9" customWidth="1"/>
@@ -8653,6 +8668,29 @@
         <v>606</v>
       </c>
     </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A182" s="9" t="s">
+        <v>610</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="F182" s="11">
+        <v>2023</v>
+      </c>
+      <c r="G182" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="H182" s="11" t="s">
+        <v>548</v>
+      </c>
+      <c r="I182" s="9" t="s">
+        <v>613</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <protectedRanges>
@@ -8673,27 +8711,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cf10023c-c1e1-4ca5-baf6-bad6626b84e9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_Flow_SignoffStatus xmlns="cf10023c-c1e1-4ca5-baf6-bad6626b84e9" xsi:nil="true"/>
-    <TaxCatchAll xmlns="40b16217-7e26-4dce-af97-68eaad0f1932" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CD0C5713D8B49840BA44FC47BC25FC9F" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d6c26ebffaa8bbd830e647f783d3198d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cf10023c-c1e1-4ca5-baf6-bad6626b84e9" xmlns:ns3="40b16217-7e26-4dce-af97-68eaad0f1932" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f461dd4a85cef57f3309d1104a6214f5" ns2:_="" ns3:_="">
     <xsd:import namespace="cf10023c-c1e1-4ca5-baf6-bad6626b84e9"/>
@@ -8928,26 +8945,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6269017F-E5DB-403C-81C5-BBF155D4F583}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="cf10023c-c1e1-4ca5-baf6-bad6626b84e9"/>
-    <ds:schemaRef ds:uri="40b16217-7e26-4dce-af97-68eaad0f1932"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{172B3EEB-21ED-4F96-BCDA-03252FF4BB1C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cf10023c-c1e1-4ca5-baf6-bad6626b84e9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_Flow_SignoffStatus xmlns="cf10023c-c1e1-4ca5-baf6-bad6626b84e9" xsi:nil="true"/>
+    <TaxCatchAll xmlns="40b16217-7e26-4dce-af97-68eaad0f1932" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5A73F1C-4F4E-45A2-8E7F-3EB53382C2D3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8964,4 +8983,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{172B3EEB-21ED-4F96-BCDA-03252FF4BB1C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6269017F-E5DB-403C-81C5-BBF155D4F583}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cf10023c-c1e1-4ca5-baf6-bad6626b84e9"/>
+    <ds:schemaRef ds:uri="40b16217-7e26-4dce-af97-68eaad0f1932"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Fleet.xlsx
+++ b/Fleet.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MohamedShakeel\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95BB45E5-B1DD-43FE-9E68-351B02C9D9F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27EC3830-0ECB-4632-AB1E-9ADFCBF6E8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1785" yWindow="225" windowWidth="13530" windowHeight="15345" xr2:uid="{EB5E0735-E981-4D65-8766-4471E111115C}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="18615" windowHeight="13620" xr2:uid="{EB5E0735-E981-4D65-8766-4471E111115C}"/>
   </bookViews>
   <sheets>
     <sheet name="Vehicles &amp; others" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vehicles &amp; others'!$A$1:$M$175</definedName>
-    <definedName name="_xlcn.WorksheetConnection_VehiclesothersA1K1501" hidden="1">'Vehicles &amp; others'!$A$2:$L$148</definedName>
+    <definedName name="_xlcn.WorksheetConnection_VehiclesothersA1K150" hidden="1">'Vehicles &amp; others'!$A$2:$L$148</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -61,7 +61,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="Range" autoDelete="1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_VehiclesothersA1K1501"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_VehiclesothersA1K150"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -1263,9 +1263,6 @@
     <t>WMA26WZZ8HM728196</t>
   </si>
   <si>
-    <t>WMA03WZZ1DM614888</t>
-  </si>
-  <si>
     <t>WMA03WZZ7DM614894</t>
   </si>
   <si>
@@ -1915,6 +1912,9 @@
   </si>
   <si>
     <t>ST-31041</t>
+  </si>
+  <si>
+    <t>WMA03WZZ1DM614889</t>
   </si>
 </sst>
 </file>
@@ -2431,7 +2431,7 @@
         <v>145</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>146</v>
@@ -2457,7 +2457,7 @@
         <v>152</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>186</v>
@@ -2472,10 +2472,10 @@
         <v>2005</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>138</v>
@@ -2484,7 +2484,7 @@
         <v>53395</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -2492,7 +2492,7 @@
         <v>152</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>187</v>
@@ -2507,10 +2507,10 @@
         <v>2000</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>138</v>
@@ -2519,7 +2519,7 @@
         <v>55085</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -2542,10 +2542,10 @@
         <v>1999</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>138</v>
@@ -2554,7 +2554,7 @@
         <v>15104</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -2577,10 +2577,10 @@
         <v>2007</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>138</v>
@@ -2589,7 +2589,7 @@
         <v>135047</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -2597,7 +2597,7 @@
         <v>152</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>190</v>
@@ -2612,10 +2612,10 @@
         <v>2007</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>138</v>
@@ -2624,7 +2624,7 @@
         <v>133080</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -2632,7 +2632,7 @@
         <v>152</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>191</v>
@@ -2647,10 +2647,10 @@
         <v>2007</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>138</v>
@@ -2659,7 +2659,7 @@
         <v>53656</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -2667,7 +2667,7 @@
         <v>152</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>192</v>
@@ -2682,10 +2682,10 @@
         <v>2008</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>138</v>
@@ -2694,7 +2694,7 @@
         <v>61982</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -2702,7 +2702,7 @@
         <v>152</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>193</v>
@@ -2717,10 +2717,10 @@
         <v>2008</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>138</v>
@@ -2729,7 +2729,7 @@
         <v>137072</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -2737,7 +2737,7 @@
         <v>152</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>194</v>
@@ -2752,10 +2752,10 @@
         <v>2007</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>138</v>
@@ -2764,7 +2764,7 @@
         <v>61955</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -2772,7 +2772,7 @@
         <v>152</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>195</v>
@@ -2787,10 +2787,10 @@
         <v>2008</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>138</v>
@@ -2799,7 +2799,7 @@
         <v>73193</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -2807,7 +2807,7 @@
         <v>152</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>196</v>
@@ -2822,19 +2822,19 @@
         <v>2008</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>138</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -2842,7 +2842,7 @@
         <v>152</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>197</v>
@@ -2857,10 +2857,10 @@
         <v>2012</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>138</v>
@@ -2869,7 +2869,7 @@
         <v>67533</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -2877,7 +2877,7 @@
         <v>152</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>198</v>
@@ -2892,10 +2892,10 @@
         <v>2007</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>138</v>
@@ -2904,7 +2904,7 @@
         <v>137050</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -2912,7 +2912,7 @@
         <v>152</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>199</v>
@@ -2927,10 +2927,10 @@
         <v>2013</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>138</v>
@@ -2939,7 +2939,7 @@
         <v>138196</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -2947,7 +2947,7 @@
         <v>152</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>200</v>
@@ -2962,10 +2962,10 @@
         <v>2007</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>138</v>
@@ -2974,7 +2974,7 @@
         <v>67306</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -2982,7 +2982,7 @@
         <v>152</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>201</v>
@@ -2997,10 +2997,10 @@
         <v>2013</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>138</v>
@@ -3009,7 +3009,7 @@
         <v>73379</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -3017,7 +3017,7 @@
         <v>152</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>202</v>
@@ -3032,10 +3032,10 @@
         <v>2013</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>138</v>
@@ -3044,7 +3044,7 @@
         <v>135154</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -3052,7 +3052,7 @@
         <v>152</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>203</v>
@@ -3070,7 +3070,7 @@
         <v>329</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>138</v>
@@ -3079,7 +3079,7 @@
         <v>55005199</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -3087,7 +3087,7 @@
         <v>152</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>204</v>
@@ -3105,7 +3105,7 @@
         <v>329</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>138</v>
@@ -3114,7 +3114,7 @@
         <v>55005197</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -3122,7 +3122,7 @@
         <v>152</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>205</v>
@@ -3137,10 +3137,10 @@
         <v>2014</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>138</v>
@@ -3149,7 +3149,7 @@
         <v>46014</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -3157,7 +3157,7 @@
         <v>152</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>206</v>
@@ -3172,10 +3172,10 @@
         <v>2014</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>138</v>
@@ -3184,7 +3184,7 @@
         <v>45087</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -3192,7 +3192,7 @@
         <v>152</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>207</v>
@@ -3207,10 +3207,10 @@
         <v>2014</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>138</v>
@@ -3219,7 +3219,7 @@
         <v>45432</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -3227,7 +3227,7 @@
         <v>152</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>208</v>
@@ -3242,10 +3242,10 @@
         <v>2014</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>138</v>
@@ -3254,7 +3254,7 @@
         <v>45433</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -3262,7 +3262,7 @@
         <v>152</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>209</v>
@@ -3277,10 +3277,10 @@
         <v>2015</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>138</v>
@@ -3289,7 +3289,7 @@
         <v>45448</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -3297,7 +3297,7 @@
         <v>152</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>210</v>
@@ -3312,10 +3312,10 @@
         <v>2015</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>138</v>
@@ -3324,7 +3324,7 @@
         <v>45449</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -3332,7 +3332,7 @@
         <v>152</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>211</v>
@@ -3347,10 +3347,10 @@
         <v>2014</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>138</v>
@@ -3359,7 +3359,7 @@
         <v>45452</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -3367,7 +3367,7 @@
         <v>152</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>212</v>
@@ -3382,10 +3382,10 @@
         <v>2007</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>138</v>
@@ -3394,7 +3394,7 @@
         <v>135044</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -3417,10 +3417,10 @@
         <v>2007</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>138</v>
@@ -3429,7 +3429,7 @@
         <v>74746</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -3437,7 +3437,7 @@
         <v>152</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>214</v>
@@ -3452,10 +3452,10 @@
         <v>2010</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>138</v>
@@ -3464,7 +3464,7 @@
         <v>10129</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -3472,7 +3472,7 @@
         <v>152</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>215</v>
@@ -3487,10 +3487,10 @@
         <v>2016</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>138</v>
@@ -3499,7 +3499,7 @@
         <v>549566</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -3507,7 +3507,7 @@
         <v>152</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>216</v>
@@ -3522,10 +3522,10 @@
         <v>2016</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>138</v>
@@ -3534,7 +3534,7 @@
         <v>549568</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -3542,7 +3542,7 @@
         <v>152</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>217</v>
@@ -3557,10 +3557,10 @@
         <v>2016</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>138</v>
@@ -3569,7 +3569,7 @@
         <v>549753</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -3577,7 +3577,7 @@
         <v>152</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>218</v>
@@ -3592,10 +3592,10 @@
         <v>2016</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>138</v>
@@ -3604,7 +3604,7 @@
         <v>549754</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -3612,7 +3612,7 @@
         <v>152</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>219</v>
@@ -3627,10 +3627,10 @@
         <v>2008</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>138</v>
@@ -3639,7 +3639,7 @@
         <v>62274</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -3662,10 +3662,10 @@
         <v>2017</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>138</v>
@@ -3674,7 +3674,7 @@
         <v>549840</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -3697,10 +3697,10 @@
         <v>2017</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>138</v>
@@ -3709,7 +3709,7 @@
         <v>549839</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -3732,10 +3732,10 @@
         <v>2017</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>138</v>
@@ -3744,7 +3744,7 @@
         <v>549877</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -3767,10 +3767,10 @@
         <v>2017</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>138</v>
@@ -3779,7 +3779,7 @@
         <v>549861</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -3787,7 +3787,7 @@
         <v>152</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>224</v>
@@ -3802,10 +3802,10 @@
         <v>2010</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>138</v>
@@ -3814,7 +3814,7 @@
         <v>10127</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -3837,10 +3837,10 @@
         <v>2008</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>138</v>
@@ -3849,7 +3849,7 @@
         <v>62059</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -3872,10 +3872,10 @@
         <v>2008</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>138</v>
@@ -3884,7 +3884,7 @@
         <v>62022</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -3907,10 +3907,10 @@
         <v>2017</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>138</v>
@@ -3919,7 +3919,7 @@
         <v>35321</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -3942,19 +3942,19 @@
         <v>2023</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>138</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -3977,19 +3977,19 @@
         <v>2023</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>138</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -4012,19 +4012,19 @@
         <v>2023</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>138</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -4047,19 +4047,19 @@
         <v>2023</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>138</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -4082,19 +4082,19 @@
         <v>2023</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>138</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -4117,19 +4117,19 @@
         <v>2023</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>138</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -4152,19 +4152,19 @@
         <v>2023</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>138</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -4187,19 +4187,19 @@
         <v>2023</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>138</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -4222,19 +4222,19 @@
         <v>2010</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>138</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -4257,19 +4257,19 @@
         <v>2023</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>138</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -4292,19 +4292,19 @@
         <v>2023</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>138</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -4327,19 +4327,19 @@
         <v>2023</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>138</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -4362,19 +4362,19 @@
         <v>2023</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>138</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -4397,19 +4397,19 @@
         <v>2023</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>138</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -4432,19 +4432,19 @@
         <v>2023</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H58" s="10" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>138</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -4467,19 +4467,19 @@
         <v>2023</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>138</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -4502,19 +4502,19 @@
         <v>2023</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>138</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -4537,19 +4537,19 @@
         <v>2023</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>138</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -4572,19 +4572,19 @@
         <v>2023</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>138</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -4607,19 +4607,19 @@
         <v>2023</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>138</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -4642,19 +4642,19 @@
         <v>2023</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>138</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
@@ -4677,19 +4677,19 @@
         <v>2021</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>138</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -4712,10 +4712,10 @@
         <v>2022</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H66" s="10" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>138</v>
@@ -4724,7 +4724,7 @@
         <v>138</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -4747,10 +4747,10 @@
         <v>2025</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>138</v>
@@ -4759,7 +4759,7 @@
         <v>138</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
@@ -4767,7 +4767,7 @@
         <v>152</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>252</v>
@@ -4798,7 +4798,7 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>167</v>
@@ -4816,10 +4816,10 @@
         <v>2006</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>355</v>
@@ -4828,13 +4828,13 @@
         <v>138</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L69" s="2"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>167</v>
@@ -4852,7 +4852,7 @@
         <v>2006</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H70" s="10" t="s">
         <v>138</v>
@@ -4870,7 +4870,7 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>167</v>
@@ -4888,7 +4888,7 @@
         <v>2006</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H71" s="10" t="s">
         <v>138</v>
@@ -4906,7 +4906,7 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>167</v>
@@ -4924,7 +4924,7 @@
         <v>2007</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H72" s="10" t="s">
         <v>138</v>
@@ -4936,13 +4936,13 @@
         <v>138</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L72" s="2"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>167</v>
@@ -4960,7 +4960,7 @@
         <v>2007</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H73" s="10" t="s">
         <v>138</v>
@@ -4978,7 +4978,7 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>167</v>
@@ -4996,7 +4996,7 @@
         <v>2007</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H74" s="10" t="s">
         <v>138</v>
@@ -5014,7 +5014,7 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>167</v>
@@ -5032,10 +5032,10 @@
         <v>2007</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>361</v>
@@ -5044,13 +5044,13 @@
         <v>138</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L75" s="2"/>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>167</v>
@@ -5068,7 +5068,7 @@
         <v>2007</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H76" s="10" t="s">
         <v>138</v>
@@ -5086,7 +5086,7 @@
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>167</v>
@@ -5104,7 +5104,7 @@
         <v>2009</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H77" s="10" t="s">
         <v>138</v>
@@ -5116,13 +5116,13 @@
         <v>138</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L77" s="2"/>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>167</v>
@@ -5140,7 +5140,7 @@
         <v>2009</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H78" s="10" t="s">
         <v>138</v>
@@ -5158,7 +5158,7 @@
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>167</v>
@@ -5176,7 +5176,7 @@
         <v>2009</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H79" s="10" t="s">
         <v>138</v>
@@ -5194,7 +5194,7 @@
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>167</v>
@@ -5212,7 +5212,7 @@
         <v>2009</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H80" s="10" t="s">
         <v>138</v>
@@ -5230,7 +5230,7 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>168</v>
@@ -5266,7 +5266,7 @@
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>168</v>
@@ -5296,13 +5296,13 @@
         <v>138</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L82" s="2"/>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>168</v>
@@ -5332,13 +5332,13 @@
         <v>138</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L83" s="2"/>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>168</v>
@@ -5368,13 +5368,13 @@
         <v>138</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L84" s="2"/>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>169</v>
@@ -5404,13 +5404,13 @@
         <v>138</v>
       </c>
       <c r="K85" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L85" s="5"/>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>169</v>
@@ -5440,13 +5440,13 @@
         <v>138</v>
       </c>
       <c r="K86" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L86" s="5"/>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>170</v>
@@ -5476,7 +5476,7 @@
         <v>138</v>
       </c>
       <c r="K87" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L87" s="5"/>
     </row>
@@ -5512,7 +5512,7 @@
         <v>138</v>
       </c>
       <c r="K88" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L88" s="5"/>
     </row>
@@ -5548,7 +5548,7 @@
         <v>138</v>
       </c>
       <c r="K89" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L89" s="5"/>
     </row>
@@ -5584,7 +5584,7 @@
         <v>138</v>
       </c>
       <c r="K90" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L90" s="5"/>
     </row>
@@ -5620,7 +5620,7 @@
         <v>138</v>
       </c>
       <c r="K91" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L91" s="5"/>
     </row>
@@ -5656,7 +5656,7 @@
         <v>138</v>
       </c>
       <c r="K92" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L92" s="5"/>
     </row>
@@ -5692,7 +5692,7 @@
         <v>138</v>
       </c>
       <c r="K93" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L93" s="5"/>
     </row>
@@ -5728,7 +5728,7 @@
         <v>138</v>
       </c>
       <c r="K94" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L94" s="5"/>
     </row>
@@ -5764,7 +5764,7 @@
         <v>138</v>
       </c>
       <c r="K95" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L95" s="5"/>
     </row>
@@ -5800,7 +5800,7 @@
         <v>138</v>
       </c>
       <c r="K96" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L96" s="5"/>
     </row>
@@ -5836,7 +5836,7 @@
         <v>138</v>
       </c>
       <c r="K97" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L97" s="5"/>
     </row>
@@ -5872,13 +5872,13 @@
         <v>138</v>
       </c>
       <c r="K98" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L98" s="5"/>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>174</v>
@@ -5896,7 +5896,7 @@
         <v>2022</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H99" s="10" t="s">
         <v>138</v>
@@ -5908,7 +5908,7 @@
         <v>138</v>
       </c>
       <c r="K99" s="5" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L99" s="5"/>
     </row>
@@ -5944,7 +5944,7 @@
         <v>138</v>
       </c>
       <c r="K100" s="5" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L100" s="5"/>
     </row>
@@ -5980,7 +5980,7 @@
         <v>138</v>
       </c>
       <c r="K101" s="5" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L101" s="5"/>
     </row>
@@ -6016,13 +6016,13 @@
         <v>138</v>
       </c>
       <c r="K102" s="5" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L102" s="5"/>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>176</v>
@@ -6040,7 +6040,7 @@
         <v>2013</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H103" s="10" t="s">
         <v>138</v>
@@ -6052,13 +6052,13 @@
         <v>138</v>
       </c>
       <c r="K103" s="5" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L103" s="5"/>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>176</v>
@@ -6076,19 +6076,19 @@
         <v>2013</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H104" s="10" t="s">
         <v>138</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="J104" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K104" s="5" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L104" s="5"/>
     </row>
@@ -6124,7 +6124,7 @@
         <v>138</v>
       </c>
       <c r="K105" s="5" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L105" s="5"/>
     </row>
@@ -6160,7 +6160,7 @@
         <v>138</v>
       </c>
       <c r="K106" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L106" s="5"/>
     </row>
@@ -6196,7 +6196,7 @@
         <v>138</v>
       </c>
       <c r="K107" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L107" s="5"/>
     </row>
@@ -6232,7 +6232,7 @@
         <v>138</v>
       </c>
       <c r="K108" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L108" s="5"/>
     </row>
@@ -6268,7 +6268,7 @@
         <v>138</v>
       </c>
       <c r="K109" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L109" s="5"/>
     </row>
@@ -6304,7 +6304,7 @@
         <v>138</v>
       </c>
       <c r="K110" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L110" s="5"/>
     </row>
@@ -6340,13 +6340,13 @@
         <v>138</v>
       </c>
       <c r="K111" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L111" s="5"/>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>176</v>
@@ -6364,7 +6364,7 @@
         <v>2024</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H112" s="10" t="s">
         <v>138</v>
@@ -6376,7 +6376,7 @@
         <v>138</v>
       </c>
       <c r="K112" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L112" s="5"/>
     </row>
@@ -6482,7 +6482,7 @@
         <v>138</v>
       </c>
       <c r="K115" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L115" s="4"/>
     </row>
@@ -6518,7 +6518,7 @@
         <v>138</v>
       </c>
       <c r="K116" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L116" s="4"/>
     </row>
@@ -6548,13 +6548,13 @@
         <v>138</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>397</v>
+        <v>614</v>
       </c>
       <c r="J117" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K117" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L117" s="4"/>
     </row>
@@ -6584,13 +6584,13 @@
         <v>138</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="J118" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K118" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L118" s="4"/>
     </row>
@@ -6620,13 +6620,13 @@
         <v>138</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="J119" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K119" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L119" s="4"/>
     </row>
@@ -6656,13 +6656,13 @@
         <v>138</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J120" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K120" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L120" s="4"/>
     </row>
@@ -6692,13 +6692,13 @@
         <v>138</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="J121" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K121" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L121" s="4"/>
     </row>
@@ -6728,13 +6728,13 @@
         <v>138</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="J122" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K122" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L122" s="4"/>
     </row>
@@ -6764,13 +6764,13 @@
         <v>138</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="J123" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K123" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L123" s="4"/>
     </row>
@@ -6800,13 +6800,13 @@
         <v>138</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J124" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K124" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L124" s="4"/>
     </row>
@@ -6836,13 +6836,13 @@
         <v>138</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="J125" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K125" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L125" s="4"/>
     </row>
@@ -6872,13 +6872,13 @@
         <v>138</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="J126" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K126" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L126" s="4"/>
     </row>
@@ -6908,13 +6908,13 @@
         <v>138</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="J127" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K127" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L127" s="4"/>
     </row>
@@ -6938,19 +6938,19 @@
         <v>2023</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H128" s="10" t="s">
         <v>138</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="J128" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K128" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L128" s="4"/>
     </row>
@@ -6974,19 +6974,19 @@
         <v>2023</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H129" s="10" t="s">
         <v>138</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="J129" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K129" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L129" s="4"/>
     </row>
@@ -7010,19 +7010,19 @@
         <v>2023</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H130" s="10" t="s">
         <v>138</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="J130" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K130" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L130" s="4"/>
     </row>
@@ -7050,13 +7050,13 @@
         <v>138</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="J131" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K131" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L131" s="4"/>
     </row>
@@ -7084,13 +7084,13 @@
         <v>138</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="J132" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K132" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L132" s="4"/>
     </row>
@@ -7118,13 +7118,13 @@
         <v>138</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="J133" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K133" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L133" s="4"/>
     </row>
@@ -7152,13 +7152,13 @@
         <v>138</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="J134" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K134" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L134" s="4"/>
     </row>
@@ -7186,13 +7186,13 @@
         <v>138</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="J135" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K135" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L135" s="4"/>
     </row>
@@ -7220,13 +7220,13 @@
         <v>138</v>
       </c>
       <c r="I136" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="J136" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K136" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L136" s="4"/>
     </row>
@@ -7254,13 +7254,13 @@
         <v>138</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="J137" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K137" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L137" s="4"/>
     </row>
@@ -7288,13 +7288,13 @@
         <v>138</v>
       </c>
       <c r="I138" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="J138" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K138" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L138" s="4"/>
     </row>
@@ -7322,13 +7322,13 @@
         <v>138</v>
       </c>
       <c r="I139" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="J139" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K139" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L139" s="4"/>
     </row>
@@ -7356,13 +7356,13 @@
         <v>138</v>
       </c>
       <c r="I140" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J140" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K140" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L140" s="4"/>
     </row>
@@ -7390,13 +7390,13 @@
         <v>138</v>
       </c>
       <c r="I141" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="J141" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K141" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L141" s="4"/>
     </row>
@@ -7424,13 +7424,13 @@
         <v>138</v>
       </c>
       <c r="I142" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="J142" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K142" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L142" s="4"/>
     </row>
@@ -7458,13 +7458,13 @@
         <v>138</v>
       </c>
       <c r="I143" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J143" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K143" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L143" s="4"/>
     </row>
@@ -7492,13 +7492,13 @@
         <v>138</v>
       </c>
       <c r="I144" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="J144" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K144" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L144" s="4"/>
     </row>
@@ -7526,13 +7526,13 @@
         <v>138</v>
       </c>
       <c r="I145" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="J145" s="3" t="s">
         <v>138</v>
       </c>
       <c r="K145" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L145" s="4"/>
     </row>
@@ -7541,7 +7541,7 @@
         <v>152</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>322</v>
@@ -7590,13 +7590,13 @@
         <v>2023</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H147" s="10" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="I147" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>138</v>
@@ -7611,7 +7611,7 @@
         <v>152</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>324</v>
@@ -7682,10 +7682,10 @@
         <v>138</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E150" s="3" t="s">
         <v>138</v>
@@ -7714,10 +7714,10 @@
         <v>138</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E151" s="3" t="s">
         <v>138</v>
@@ -7743,22 +7743,22 @@
         <v>152</v>
       </c>
       <c r="B152" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G152" s="9" t="s">
         <v>521</v>
       </c>
-      <c r="C152" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="D152" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="E152" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="G152" s="9" t="s">
-        <v>522</v>
-      </c>
       <c r="H152" s="11" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="I152" s="9" t="s">
         <v>138</v>
@@ -7775,22 +7775,22 @@
         <v>152</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E153" s="3" t="s">
         <v>138</v>
       </c>
       <c r="G153" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H153" s="11" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="I153" s="9" t="s">
         <v>138</v>
@@ -7807,22 +7807,22 @@
         <v>152</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E154" s="3" t="s">
         <v>138</v>
       </c>
       <c r="G154" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H154" s="11" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="I154" s="9" t="s">
         <v>138</v>
@@ -7839,22 +7839,22 @@
         <v>152</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E155" s="3" t="s">
         <v>138</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H155" s="11" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="I155" s="9" t="s">
         <v>138</v>
@@ -7874,10 +7874,10 @@
         <v>138</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E156" s="3" t="s">
         <v>138</v>
@@ -7906,10 +7906,10 @@
         <v>138</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E157" s="3" t="s">
         <v>138</v>
@@ -7938,10 +7938,10 @@
         <v>138</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E158" s="3" t="s">
         <v>138</v>
@@ -7970,10 +7970,10 @@
         <v>138</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E159" s="3" t="s">
         <v>138</v>
@@ -7999,13 +7999,13 @@
         <v>152</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E160" s="3" t="s">
         <v>138</v>
@@ -8034,10 +8034,10 @@
         <v>138</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E161" s="3" t="s">
         <v>138</v>
@@ -8066,10 +8066,10 @@
         <v>138</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E162" s="3" t="s">
         <v>138</v>
@@ -8098,10 +8098,10 @@
         <v>138</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E163" s="3" t="s">
         <v>138</v>
@@ -8127,22 +8127,22 @@
         <v>152</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E164" s="3" t="s">
         <v>138</v>
       </c>
       <c r="G164" s="9" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H164" s="11" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="I164" s="9" t="s">
         <v>138</v>
@@ -8159,22 +8159,22 @@
         <v>152</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E165" s="3" t="s">
         <v>138</v>
       </c>
       <c r="G165" s="9" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H165" s="11" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="I165" s="9" t="s">
         <v>138</v>
@@ -8194,10 +8194,10 @@
         <v>138</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E166" s="3" t="s">
         <v>138</v>
@@ -8226,10 +8226,10 @@
         <v>138</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E167" s="3" t="s">
         <v>138</v>
@@ -8258,10 +8258,10 @@
         <v>138</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E168" s="3" t="s">
         <v>138</v>
@@ -8284,31 +8284,31 @@
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" s="9" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>170</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E169" s="3">
         <v>79713</v>
       </c>
       <c r="G169" s="9" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H169" s="11" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I169" s="9" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="J169" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="K169" s="3" t="s">
         <v>138</v>
@@ -8316,31 +8316,31 @@
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" s="9" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>170</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E170" s="3">
         <v>79717</v>
       </c>
       <c r="G170" s="9" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H170" s="11" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I170" s="9" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="J170" s="3" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="K170" s="3" t="s">
         <v>138</v>
@@ -8348,28 +8348,28 @@
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="B171" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="B171" s="3" t="s">
-        <v>532</v>
-      </c>
       <c r="C171" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E171" s="3">
         <v>79684</v>
       </c>
       <c r="G171" s="9" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H171" s="11" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I171" s="9" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J171" s="3" t="s">
         <v>138</v>
@@ -8380,16 +8380,16 @@
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" s="9" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>168</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E172" s="3">
         <v>80282</v>
@@ -8398,27 +8398,27 @@
         <v>2025</v>
       </c>
       <c r="G172" s="9" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H172" s="11" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="I172" s="9" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" s="9" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>168</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E173" s="3">
         <v>80265</v>
@@ -8427,27 +8427,27 @@
         <v>2025</v>
       </c>
       <c r="G173" s="9" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H173" s="11" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="I173" s="9" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" s="9" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>168</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E174" s="3">
         <v>80281</v>
@@ -8456,27 +8456,27 @@
         <v>2025</v>
       </c>
       <c r="G174" s="9" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H174" s="11" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="I174" s="9" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" s="9" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>168</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E175" s="3">
         <v>80280</v>
@@ -8485,27 +8485,27 @@
         <v>2025</v>
       </c>
       <c r="G175" s="9" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H175" s="11" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="I175" s="9" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" s="9" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>168</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E176" s="3">
         <v>80263</v>
@@ -8514,27 +8514,27 @@
         <v>2025</v>
       </c>
       <c r="G176" s="9" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H176" s="11" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="I176" s="9" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="9" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>168</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E177" s="3">
         <v>80283</v>
@@ -8543,27 +8543,27 @@
         <v>2025</v>
       </c>
       <c r="G177" s="9" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H177" s="11" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="I177" s="9" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="9" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>168</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E178" s="3">
         <v>80266</v>
@@ -8572,27 +8572,27 @@
         <v>2025</v>
       </c>
       <c r="G178" s="9" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H178" s="11" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I178" s="9" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="9" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>168</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E179" s="3">
         <v>80268</v>
@@ -8601,27 +8601,27 @@
         <v>2025</v>
       </c>
       <c r="G179" s="9" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H179" s="11" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I179" s="9" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="9" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>168</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E180" s="3">
         <v>80270</v>
@@ -8630,27 +8630,27 @@
         <v>2025</v>
       </c>
       <c r="G180" s="9" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H180" s="11" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I180" s="9" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="9" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>168</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E181" s="3">
         <v>80267</v>
@@ -8659,36 +8659,36 @@
         <v>2025</v>
       </c>
       <c r="G181" s="9" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H181" s="11" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I181" s="9" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="9" t="s">
+        <v>609</v>
+      </c>
+      <c r="B182" s="3" t="s">
         <v>610</v>
       </c>
-      <c r="B182" s="3" t="s">
-        <v>611</v>
-      </c>
       <c r="C182" s="3" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="F182" s="11">
         <v>2023</v>
       </c>
       <c r="G182" s="9" t="s">
+        <v>611</v>
+      </c>
+      <c r="H182" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="I182" s="9" t="s">
         <v>612</v>
-      </c>
-      <c r="H182" s="11" t="s">
-        <v>548</v>
-      </c>
-      <c r="I182" s="9" t="s">
-        <v>613</v>
       </c>
     </row>
   </sheetData>
@@ -8711,6 +8711,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cf10023c-c1e1-4ca5-baf6-bad6626b84e9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_Flow_SignoffStatus xmlns="cf10023c-c1e1-4ca5-baf6-bad6626b84e9" xsi:nil="true"/>
+    <TaxCatchAll xmlns="40b16217-7e26-4dce-af97-68eaad0f1932" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CD0C5713D8B49840BA44FC47BC25FC9F" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d6c26ebffaa8bbd830e647f783d3198d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cf10023c-c1e1-4ca5-baf6-bad6626b84e9" xmlns:ns3="40b16217-7e26-4dce-af97-68eaad0f1932" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f461dd4a85cef57f3309d1104a6214f5" ns2:_="" ns3:_="">
     <xsd:import namespace="cf10023c-c1e1-4ca5-baf6-bad6626b84e9"/>
@@ -8945,28 +8966,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6269017F-E5DB-403C-81C5-BBF155D4F583}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cf10023c-c1e1-4ca5-baf6-bad6626b84e9"/>
+    <ds:schemaRef ds:uri="40b16217-7e26-4dce-af97-68eaad0f1932"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cf10023c-c1e1-4ca5-baf6-bad6626b84e9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_Flow_SignoffStatus xmlns="cf10023c-c1e1-4ca5-baf6-bad6626b84e9" xsi:nil="true"/>
-    <TaxCatchAll xmlns="40b16217-7e26-4dce-af97-68eaad0f1932" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{172B3EEB-21ED-4F96-BCDA-03252FF4BB1C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5A73F1C-4F4E-45A2-8E7F-3EB53382C2D3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8983,23 +9002,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{172B3EEB-21ED-4F96-BCDA-03252FF4BB1C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6269017F-E5DB-403C-81C5-BBF155D4F583}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="cf10023c-c1e1-4ca5-baf6-bad6626b84e9"/>
-    <ds:schemaRef ds:uri="40b16217-7e26-4dce-af97-68eaad0f1932"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Fleet.xlsx
+++ b/Fleet.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MohamedShakeel\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MohamedShakeel\Downloads\WIP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27EC3830-0ECB-4632-AB1E-9ADFCBF6E8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E73B2AB0-0B9A-4A16-9B54-8612DF311718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="18615" windowHeight="13620" xr2:uid="{EB5E0735-E981-4D65-8766-4471E111115C}"/>
+    <workbookView xWindow="195" yWindow="105" windowWidth="17910" windowHeight="14235" xr2:uid="{EB5E0735-E981-4D65-8766-4471E111115C}"/>
   </bookViews>
   <sheets>
     <sheet name="Vehicles &amp; others" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vehicles &amp; others'!$A$1:$M$175</definedName>
-    <definedName name="_xlcn.WorksheetConnection_VehiclesothersA1K150" hidden="1">'Vehicles &amp; others'!$A$2:$L$148</definedName>
+    <definedName name="_xlcn.WorksheetConnection_VehiclesothersA1K1501" hidden="1">'Vehicles &amp; others'!$A$2:$L$148</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -61,7 +61,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="Range" autoDelete="1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_VehiclesothersA1K150"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_VehiclesothersA1K1501"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1615" uniqueCount="625">
   <si>
     <t>QAIG-AT-18</t>
   </si>
@@ -1915,6 +1915,36 @@
   </si>
   <si>
     <t>WMA03WZZ1DM614889</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> UD TRUCKS</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CWE350</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> JPCZYMODXTT046495</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> JPCZYMOD3TT054947</t>
+  </si>
+  <si>
+    <t>12T</t>
+  </si>
+  <si>
+    <t>T-32138</t>
+  </si>
+  <si>
+    <t>T-32139</t>
+  </si>
+  <si>
+    <t>BOOM TRUCK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D25J2107 </t>
+  </si>
+  <si>
+    <t>D25L2123</t>
   </si>
 </sst>
 </file>
@@ -2395,7 +2425,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6460FE9F-EF3B-4D4D-BCC7-D162649A6FCD}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:L182"/>
+  <dimension ref="A1:L184"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.85546875" style="9" customWidth="1"/>
@@ -8523,7 +8553,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177" s="9" t="s">
         <v>530</v>
       </c>
@@ -8552,7 +8582,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178" s="9" t="s">
         <v>530</v>
       </c>
@@ -8581,7 +8611,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179" s="9" t="s">
         <v>530</v>
       </c>
@@ -8610,7 +8640,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180" s="9" t="s">
         <v>530</v>
       </c>
@@ -8639,7 +8669,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181" s="9" t="s">
         <v>530</v>
       </c>
@@ -8668,7 +8698,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182" s="9" t="s">
         <v>609</v>
       </c>
@@ -8689,6 +8719,64 @@
       </c>
       <c r="I182" s="9" t="s">
         <v>612</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A183" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="E183" s="3">
+        <v>71064</v>
+      </c>
+      <c r="F183" s="11">
+        <v>2026</v>
+      </c>
+      <c r="G183" s="9" t="s">
+        <v>616</v>
+      </c>
+      <c r="H183" s="11" t="s">
+        <v>619</v>
+      </c>
+      <c r="I183" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="J183" s="3" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A184" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="E184" s="3">
+        <v>71216</v>
+      </c>
+      <c r="F184" s="11">
+        <v>2026</v>
+      </c>
+      <c r="G184" s="9" t="s">
+        <v>616</v>
+      </c>
+      <c r="H184" s="11" t="s">
+        <v>619</v>
+      </c>
+      <c r="I184" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="J184" s="3" t="s">
+        <v>623</v>
       </c>
     </row>
   </sheetData>
@@ -8711,27 +8799,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cf10023c-c1e1-4ca5-baf6-bad6626b84e9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_Flow_SignoffStatus xmlns="cf10023c-c1e1-4ca5-baf6-bad6626b84e9" xsi:nil="true"/>
-    <TaxCatchAll xmlns="40b16217-7e26-4dce-af97-68eaad0f1932" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CD0C5713D8B49840BA44FC47BC25FC9F" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d6c26ebffaa8bbd830e647f783d3198d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cf10023c-c1e1-4ca5-baf6-bad6626b84e9" xmlns:ns3="40b16217-7e26-4dce-af97-68eaad0f1932" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f461dd4a85cef57f3309d1104a6214f5" ns2:_="" ns3:_="">
     <xsd:import namespace="cf10023c-c1e1-4ca5-baf6-bad6626b84e9"/>
@@ -8966,26 +9033,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6269017F-E5DB-403C-81C5-BBF155D4F583}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="cf10023c-c1e1-4ca5-baf6-bad6626b84e9"/>
-    <ds:schemaRef ds:uri="40b16217-7e26-4dce-af97-68eaad0f1932"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{172B3EEB-21ED-4F96-BCDA-03252FF4BB1C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cf10023c-c1e1-4ca5-baf6-bad6626b84e9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_Flow_SignoffStatus xmlns="cf10023c-c1e1-4ca5-baf6-bad6626b84e9" xsi:nil="true"/>
+    <TaxCatchAll xmlns="40b16217-7e26-4dce-af97-68eaad0f1932" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5A73F1C-4F4E-45A2-8E7F-3EB53382C2D3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9002,4 +9071,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{172B3EEB-21ED-4F96-BCDA-03252FF4BB1C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6269017F-E5DB-403C-81C5-BBF155D4F583}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cf10023c-c1e1-4ca5-baf6-bad6626b84e9"/>
+    <ds:schemaRef ds:uri="40b16217-7e26-4dce-af97-68eaad0f1932"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>